--- a/artfynd/A 53869-2024 artfynd.xlsx
+++ b/artfynd/A 53869-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121253495</v>
       </c>
       <c r="B2" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53869-2024 artfynd.xlsx
+++ b/artfynd/A 53869-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121253495</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53869-2024 artfynd.xlsx
+++ b/artfynd/A 53869-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121253495</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>57724</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53869-2024 artfynd.xlsx
+++ b/artfynd/A 53869-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121253495</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>57725</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53869-2024 artfynd.xlsx
+++ b/artfynd/A 53869-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -808,6 +808,113 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>132567047</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Torparneskärr, Tullgarn, Vagnhärad, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>644900</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6540401</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Johan Njunjes</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johan Njunjes</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53869-2024 artfynd.xlsx
+++ b/artfynd/A 53869-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>132567047</v>
       </c>
       <c r="B3" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53869-2024 artfynd.xlsx
+++ b/artfynd/A 53869-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>132567047</v>
       </c>
       <c r="B3" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53869-2024 artfynd.xlsx
+++ b/artfynd/A 53869-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>132567047</v>
       </c>
       <c r="B3" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53869-2024 artfynd.xlsx
+++ b/artfynd/A 53869-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121253495</v>
+        <v>55401919</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,56 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Slagkärr, Vretstugan, Srm</t>
+          <t>Sumpblandskog SV Sandhälla, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>646008</v>
+        <v>645683</v>
       </c>
       <c r="R2" t="n">
-        <v>6540704</v>
+        <v>6540694</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2015-04-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2015-04-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Enstaka ex</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,30 +762,30 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Gräsgranskog</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Njunjes</t>
+          <t>Anders Haglund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Njunjes</t>
+          <t>Ekoplan Ekologigruppen, Johan Allmér</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132567047</v>
+        <v>134456248</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>101974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,34 +793,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220075</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Torparneskärr, Tullgarn, Vagnhärad, Srm</t>
+          <t>Sandhällamossen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>644900</v>
+        <v>645627</v>
       </c>
       <c r="R3" t="n">
-        <v>6540401</v>
+        <v>6540674</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,22 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,44 +891,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Njunjes</t>
+          <t>Hanna Mellgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Njunjes</t>
+          <t>Hanna Mellgren, Alexandra Holmgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134214861</v>
+        <v>121253495</v>
       </c>
       <c r="B4" t="n">
-        <v>57125</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102932</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,7 +936,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>hona</t>
@@ -959,23 +948,22 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kulltäppans våtmark, Srm</t>
+          <t>Slagkärr, Vretstugan, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>644902</v>
+        <v>646008</v>
       </c>
       <c r="R4" t="n">
-        <v>6540494</v>
+        <v>6540704</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +987,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,23 +1013,379 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Gräsgranskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Johan Njunjes</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johan Njunjes</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132567047</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Torparneskärr, Tullgarn, Vagnhärad, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>644900</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6540401</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Njunjes</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johan Njunjes</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134214857</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57125</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102932</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kricka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Anas crecca</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kulltäppans våtmark, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>644902</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6540494</v>
+      </c>
+      <c r="S6" t="n">
+        <v>75</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Göran Andersson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Göran Andersson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Klubb Tomt 100</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134415972</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56706</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fjolårsunge</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kulltäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>645146</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6540409</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hanna Mellgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hanna Mellgren, Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53869-2024 artfynd.xlsx
+++ b/artfynd/A 53869-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55401919</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456248</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1031,6 +1046,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121253495</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132567047</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1265,6 +1290,11 @@
           <t>Klubb Tomt 100</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134214857</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1386,8 +1416,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134415972</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 53869-2024 artfynd.xlsx
+++ b/artfynd/A 53869-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1166,48 +1166,44 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134214857</v>
+        <v>135594495</v>
       </c>
       <c r="B6" t="n">
-        <v>57125</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102932</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1247,22 +1243,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,23 +1281,19 @@
           <t>Göran Andersson</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Klubb Tomt 100</t>
-        </is>
-      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134214857</t>
+          <t>https://artportalen.se/Sighting/135594495</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134415972</v>
+        <v>134214857</v>
       </c>
       <c r="B7" t="n">
-        <v>56706</v>
+        <v>57125</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,51 +1301,53 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206046</v>
+        <v>102932</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fjolårsunge</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kulltäppan, Srm</t>
+          <t>Kulltäppans våtmark, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>645146</v>
+        <v>644902</v>
       </c>
       <c r="R7" t="n">
-        <v>6540409</v>
+        <v>6540494</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1377,22 +1371,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,16 +1401,270 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Göran Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Göran Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Klubb Tomt 100</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134214857</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135594503</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57386</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kulltäppans våtmark, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>644902</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6540494</v>
+      </c>
+      <c r="S8" t="n">
+        <v>75</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Göran Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Göran Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135594503</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134415972</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56706</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fjolårsunge</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kulltäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>645146</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6540409</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Hanna Mellgren</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Hanna Mellgren, Alexandra Holmgren</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr">
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134415972</t>
         </is>
@@ -1430,6 +1678,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53869-2024 artfynd.xlsx
+++ b/artfynd/A 53869-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1169,7 +1169,7 @@
         <v>135594495</v>
       </c>
       <c r="B6" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,27 +1290,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134214857</v>
+        <v>135673517</v>
       </c>
       <c r="B7" t="n">
-        <v>57125</v>
+        <v>58066</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102932</v>
+        <v>102626</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1324,16 +1324,8 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1371,22 +1363,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,23 +1391,19 @@
           <t>Göran Andersson</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Klubb Tomt 100</t>
-        </is>
-      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134214857</t>
+          <t>https://artportalen.se/Sighting/135673517</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135594503</v>
+        <v>134214857</v>
       </c>
       <c r="B8" t="n">
-        <v>57386</v>
+        <v>57125</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,33 +1411,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102954</v>
+        <v>102932</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1499,22 +1481,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1537,19 +1519,23 @@
           <t>Göran Andersson</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Klubb Tomt 100</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135594503</t>
+          <t>https://artportalen.se/Sighting/134214857</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134415972</v>
+        <v>135594503</v>
       </c>
       <c r="B9" t="n">
-        <v>56706</v>
+        <v>57391</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,16 +1543,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>206046</v>
+        <v>102954</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1579,29 +1565,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fjolårsunge</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kulltäppan, Srm</t>
+          <t>Kulltäppans våtmark, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>645146</v>
+        <v>644902</v>
       </c>
       <c r="R9" t="n">
-        <v>6540409</v>
+        <v>6540494</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1625,22 +1609,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1655,16 +1639,142 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Hanna Mellgren</t>
+          <t>Göran Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hanna Mellgren, Alexandra Holmgren</t>
+          <t>Göran Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135594503</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134415972</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56706</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fjolårsunge</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kulltäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>645146</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6540409</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Hanna Mellgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Hanna Mellgren, Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134415972</t>
         </is>
@@ -1680,6 +1790,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53869-2024 artfynd.xlsx
+++ b/artfynd/A 53869-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1166,48 +1166,44 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134214857</v>
+        <v>135594495</v>
       </c>
       <c r="B6" t="n">
-        <v>57125</v>
+        <v>57977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102932</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1247,22 +1243,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,75 +1281,65 @@
           <t>Göran Andersson</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Klubb Tomt 100</t>
-        </is>
-      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134214857</t>
+          <t>https://artportalen.se/Sighting/135594495</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134415972</v>
+        <v>135673517</v>
       </c>
       <c r="B7" t="n">
-        <v>56706</v>
+        <v>58066</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206046</v>
+        <v>102626</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fjolårsunge</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kulltäppan, Srm</t>
+          <t>Kulltäppans våtmark, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>645146</v>
+        <v>644902</v>
       </c>
       <c r="R7" t="n">
-        <v>6540409</v>
+        <v>6540494</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1377,22 +1363,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,16 +1383,398 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hanna Mellgren</t>
+          <t>Göran Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hanna Mellgren, Alexandra Holmgren</t>
+          <t>Göran Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135673517</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134214857</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57125</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102932</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kricka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Anas crecca</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kulltäppans våtmark, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>644902</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6540494</v>
+      </c>
+      <c r="S8" t="n">
+        <v>75</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Göran Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Göran Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Klubb Tomt 100</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134214857</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135594503</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57391</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kulltäppans våtmark, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>644902</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6540494</v>
+      </c>
+      <c r="S9" t="n">
+        <v>75</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Göran Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Göran Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135594503</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134415972</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56706</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fjolårsunge</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kulltäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>645146</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6540409</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Hanna Mellgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Hanna Mellgren, Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134415972</t>
         </is>
@@ -1430,6 +1788,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53869-2024 artfynd.xlsx
+++ b/artfynd/A 53869-2024 artfynd.xlsx
@@ -1169,7 +1169,7 @@
         <v>135594495</v>
       </c>
       <c r="B6" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>135673517</v>
       </c>
       <c r="B7" t="n">
-        <v>58066</v>
+        <v>58068</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>135594503</v>
       </c>
       <c r="B9" t="n">
-        <v>57391</v>
+        <v>57393</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 53869-2024 artfynd.xlsx
+++ b/artfynd/A 53869-2024 artfynd.xlsx
@@ -1293,7 +1293,7 @@
         <v>135673517</v>
       </c>
       <c r="B7" t="n">
-        <v>58068</v>
+        <v>58069</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 53869-2024 artfynd.xlsx
+++ b/artfynd/A 53869-2024 artfynd.xlsx
@@ -1293,7 +1293,7 @@
         <v>135673517</v>
       </c>
       <c r="B7" t="n">
-        <v>58069</v>
+        <v>58073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 53869-2024 artfynd.xlsx
+++ b/artfynd/A 53869-2024 artfynd.xlsx
@@ -1293,7 +1293,7 @@
         <v>135673517</v>
       </c>
       <c r="B7" t="n">
-        <v>58073</v>
+        <v>58074</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
